--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>7040</x:v>
+        <x:v>9040</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>149761</x:v>
+        <x:v>155761</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>7040</x:v>
+        <x:v>9040</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3151</x:v>
+        <x:v>3271</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>167688</x:v>
+        <x:v>177808</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>155761</x:v>
+        <x:v>169261</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3271</x:v>
+        <x:v>3541</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>177808</x:v>
+        <x:v>191578</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>540</x:v>
+        <x:v>640</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>169261</x:v>
+        <x:v>173761</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3541</x:v>
+        <x:v>3631</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>191578</x:v>
+        <x:v>196268</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>640</x:v>
+        <x:v>1230</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>9040</x:v>
+        <x:v>14080</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2043,7 +2043,7 @@
       <x:c r="N18" s="56" t="s"/>
       <x:c r="O18" s="58" t="s"/>
       <x:c r="P18" s="60" t="n">
-        <x:v>150</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>173761</x:v>
+        <x:v>227581</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>9040</x:v>
+        <x:v>14080</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3631</x:v>
+        <x:v>5011</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>196268</x:v>
+        <x:v>262238</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>227581</x:v>
+        <x:v>229081</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5011</x:v>
+        <x:v>5041</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>262238</x:v>
+        <x:v>263768</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>229081</x:v>
+        <x:v>229801</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5041</x:v>
+        <x:v>5071</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>263768</x:v>
+        <x:v>264518</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>14080</x:v>
+        <x:v>14580</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>229801</x:v>
+        <x:v>234301</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>14080</x:v>
+        <x:v>14580</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5071</x:v>
+        <x:v>5161</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>264518</x:v>
+        <x:v>270108</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>1230</x:v>
+        <x:v>740</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>14580</x:v>
+        <x:v>9540</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2043,7 +2043,7 @@
       <x:c r="N18" s="56" t="s"/>
       <x:c r="O18" s="58" t="s"/>
       <x:c r="P18" s="60" t="n">
-        <x:v>250</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>234301</x:v>
+        <x:v>181981</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>14580</x:v>
+        <x:v>9540</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5161</x:v>
+        <x:v>3841</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>270108</x:v>
+        <x:v>205798</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>181981</x:v>
+        <x:v>186481</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3841</x:v>
+        <x:v>3871</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>205798</x:v>
+        <x:v>210328</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>186481</x:v>
+        <x:v>184981</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3871</x:v>
+        <x:v>3901</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>210328</x:v>
+        <x:v>208858</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>184981</x:v>
+        <x:v>187981</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3901</x:v>
+        <x:v>3961</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>208858</x:v>
+        <x:v>211918</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>740</x:v>
+        <x:v>790</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3961</x:v>
+        <x:v>3991</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>211918</x:v>
+        <x:v>211998</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>187981</x:v>
+        <x:v>189481</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3991</x:v>
+        <x:v>4021</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>211998</x:v>
+        <x:v>213528</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>189481</x:v>
+        <x:v>190201</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4021</x:v>
+        <x:v>4051</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>213528</x:v>
+        <x:v>214278</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>790</x:v>
+        <x:v>890</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>0</x:v>
+        <x:v>396</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>1</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4051</x:v>
+        <x:v>4111</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>214278</x:v>
+        <x:v>215014</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>890</x:v>
+        <x:v>990</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>9540</x:v>
+        <x:v>10040</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>190201</x:v>
+        <x:v>191701</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>9540</x:v>
+        <x:v>10040</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4111</x:v>
+        <x:v>4201</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>215014</x:v>
+        <x:v>217704</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>10040</x:v>
+        <x:v>10540</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>191701</x:v>
+        <x:v>197701</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>10040</x:v>
+        <x:v>10540</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>396</x:v>
+        <x:v>828</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>181</x:v>
+        <x:v>361</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4201</x:v>
+        <x:v>4351</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>217704</x:v>
+        <x:v>225466</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>990</x:v>
+        <x:v>1040</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>10540</x:v>
+        <x:v>11040</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>197701</x:v>
+        <x:v>203701</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>10540</x:v>
+        <x:v>11040</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4351</x:v>
+        <x:v>4501</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>225466</x:v>
+        <x:v>232666</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>11040</x:v>
+        <x:v>11540</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>203701</x:v>
+        <x:v>205201</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>11040</x:v>
+        <x:v>11540</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4501</x:v>
+        <x:v>4531</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>232666</x:v>
+        <x:v>235196</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>1040</x:v>
+        <x:v>1090</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4531</x:v>
+        <x:v>4561</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>235196</x:v>
+        <x:v>235276</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>11540</x:v>
+        <x:v>13540</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>205201</x:v>
+        <x:v>211201</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>11540</x:v>
+        <x:v>13540</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4561</x:v>
+        <x:v>4681</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>235276</x:v>
+        <x:v>245396</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>211201</x:v>
+        <x:v>214861</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4681</x:v>
+        <x:v>4741</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>245396</x:v>
+        <x:v>249116</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>1090</x:v>
+        <x:v>1240</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4741</x:v>
+        <x:v>4801</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>249116</x:v>
+        <x:v>249326</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>1240</x:v>
+        <x:v>1640</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4801</x:v>
+        <x:v>4951</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>249326</x:v>
+        <x:v>249876</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>1640</x:v>
+        <x:v>1890</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>13540</x:v>
+        <x:v>14040</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>214861</x:v>
+        <x:v>216361</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>13540</x:v>
+        <x:v>14040</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2557,7 +2557,7 @@
       <x:c r="N40" s="56" t="s"/>
       <x:c r="O40" s="58" t="s"/>
       <x:c r="P40" s="60" t="n">
-        <x:v>1</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4951</x:v>
+        <x:v>5041</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>249876</x:v>
+        <x:v>252766</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>216361</x:v>
+        <x:v>217861</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5041</x:v>
+        <x:v>5071</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>252766</x:v>
+        <x:v>254296</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>1890</x:v>
+        <x:v>1990</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5071</x:v>
+        <x:v>5101</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>254296</x:v>
+        <x:v>254426</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>1990</x:v>
+        <x:v>2040</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5101</x:v>
+        <x:v>5131</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>254426</x:v>
+        <x:v>254506</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>14040</x:v>
+        <x:v>15540</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>217861</x:v>
+        <x:v>229081</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>14040</x:v>
+        <x:v>15540</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5131</x:v>
+        <x:v>5371</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>254506</x:v>
+        <x:v>268966</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>229081</x:v>
+        <x:v>233581</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5371</x:v>
+        <x:v>5461</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>268966</x:v>
+        <x:v>273556</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2557,7 +2557,7 @@
       <x:c r="N40" s="56" t="s"/>
       <x:c r="O40" s="58" t="s"/>
       <x:c r="P40" s="60" t="n">
-        <x:v>51</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>273556</x:v>
+        <x:v>273606</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>2040</x:v>
+        <x:v>2090</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>233581</x:v>
+        <x:v>234301</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5461</x:v>
+        <x:v>5521</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>273606</x:v>
+        <x:v>274436</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>234301</x:v>
+        <x:v>235021</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>274436</x:v>
+        <x:v>275156</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>235021</x:v>
+        <x:v>238021</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5521</x:v>
+        <x:v>5581</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>275156</x:v>
+        <x:v>278216</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>238021</x:v>
+        <x:v>242521</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5581</x:v>
+        <x:v>5671</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>278216</x:v>
+        <x:v>282806</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>15540</x:v>
+        <x:v>16040</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>242521</x:v>
+        <x:v>244021</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>15540</x:v>
+        <x:v>16040</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5671</x:v>
+        <x:v>5701</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>282806</x:v>
+        <x:v>285336</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>2090</x:v>
+        <x:v>2190</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>244021</x:v>
+        <x:v>250021</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5701</x:v>
+        <x:v>5881</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>285336</x:v>
+        <x:v>291616</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>250021</x:v>
+        <x:v>251521</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5881</x:v>
+        <x:v>5911</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>291616</x:v>
+        <x:v>293146</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>251521</x:v>
+        <x:v>253021</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5911</x:v>
+        <x:v>5941</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>293146</x:v>
+        <x:v>294676</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>253021</x:v>
+        <x:v>254461</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5941</x:v>
+        <x:v>6001</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>294676</x:v>
+        <x:v>296176</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>254461</x:v>
+        <x:v>258961</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6001</x:v>
+        <x:v>6091</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>296176</x:v>
+        <x:v>300766</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>258961</x:v>
+        <x:v>260461</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6091</x:v>
+        <x:v>6121</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>300766</x:v>
+        <x:v>302296</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>2190</x:v>
+        <x:v>2240</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6121</x:v>
+        <x:v>6151</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>302296</x:v>
+        <x:v>302376</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>260461</x:v>
+        <x:v>261961</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6151</x:v>
+        <x:v>6181</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>302376</x:v>
+        <x:v>303906</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>261961</x:v>
+        <x:v>267961</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6181</x:v>
+        <x:v>6301</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>303906</x:v>
+        <x:v>310026</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>2240</x:v>
+        <x:v>2866</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>16040</x:v>
+        <x:v>18120</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>267961</x:v>
+        <x:v>270961</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>16040</x:v>
+        <x:v>18120</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6301</x:v>
+        <x:v>6421</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>310026</x:v>
+        <x:v>317932</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>18120</x:v>
+        <x:v>18620</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>270961</x:v>
+        <x:v>272461</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>18120</x:v>
+        <x:v>18620</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6421</x:v>
+        <x:v>6451</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>317932</x:v>
+        <x:v>320462</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>272461</x:v>
+        <x:v>275461</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6451</x:v>
+        <x:v>6511</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>320462</x:v>
+        <x:v>323522</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>2866</x:v>
+        <x:v>2916</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6511</x:v>
+        <x:v>6541</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>323522</x:v>
+        <x:v>323602</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>2916</x:v>
+        <x:v>4836</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>18620</x:v>
+        <x:v>22220</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>18620</x:v>
+        <x:v>22220</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6541</x:v>
+        <x:v>6571</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>323602</x:v>
+        <x:v>332752</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>22220</x:v>
+        <x:v>22720</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>275461</x:v>
+        <x:v>276961</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>22220</x:v>
+        <x:v>22720</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6571</x:v>
+        <x:v>6601</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>332752</x:v>
+        <x:v>335282</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>276961</x:v>
+        <x:v>278461</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6601</x:v>
+        <x:v>6631</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>335282</x:v>
+        <x:v>336812</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>278461</x:v>
+        <x:v>288961</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6631</x:v>
+        <x:v>6781</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>336812</x:v>
+        <x:v>347462</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>288961</x:v>
+        <x:v>291961</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6781</x:v>
+        <x:v>6841</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>347462</x:v>
+        <x:v>350522</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>4836</x:v>
+        <x:v>4936</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6841</x:v>
+        <x:v>6901</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>350522</x:v>
+        <x:v>350682</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>4936</x:v>
+        <x:v>5086</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6901</x:v>
+        <x:v>6961</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>350682</x:v>
+        <x:v>350892</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>291961</x:v>
+        <x:v>294961</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6961</x:v>
+        <x:v>7021</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>350892</x:v>
+        <x:v>353952</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>294961</x:v>
+        <x:v>298681</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7021</x:v>
+        <x:v>7111</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>353952</x:v>
+        <x:v>357762</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>22720</x:v>
+        <x:v>23220</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>298681</x:v>
+        <x:v>300181</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>22720</x:v>
+        <x:v>23220</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7111</x:v>
+        <x:v>7141</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>357762</x:v>
+        <x:v>360292</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>300181</x:v>
+        <x:v>303901</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7141</x:v>
+        <x:v>7231</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>360292</x:v>
+        <x:v>364102</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>303901</x:v>
+        <x:v>305401</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7231</x:v>
+        <x:v>7261</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>364102</x:v>
+        <x:v>365632</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>305401</x:v>
+        <x:v>308401</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7261</x:v>
+        <x:v>7321</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>365632</x:v>
+        <x:v>368692</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>308401</x:v>
+        <x:v>309901</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7321</x:v>
+        <x:v>7351</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>368692</x:v>
+        <x:v>370222</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>309901</x:v>
+        <x:v>312901</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7351</x:v>
+        <x:v>7411</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>370222</x:v>
+        <x:v>373282</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>23220</x:v>
+        <x:v>23720</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>312901</x:v>
+        <x:v>314401</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>23220</x:v>
+        <x:v>23720</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7411</x:v>
+        <x:v>7441</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>373282</x:v>
+        <x:v>375812</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>314401</x:v>
+        <x:v>315901</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7441</x:v>
+        <x:v>7471</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>375812</x:v>
+        <x:v>377342</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>315901</x:v>
+        <x:v>316621</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7471</x:v>
+        <x:v>7501</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>377342</x:v>
+        <x:v>378092</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>316621</x:v>
+        <x:v>321121</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7501</x:v>
+        <x:v>7591</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>378092</x:v>
+        <x:v>382682</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>23720</x:v>
+        <x:v>25720</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>321121</x:v>
+        <x:v>333121</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>23720</x:v>
+        <x:v>25720</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7591</x:v>
+        <x:v>7831</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>382682</x:v>
+        <x:v>398922</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>25720</x:v>
+        <x:v>26220</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>333121</x:v>
+        <x:v>334621</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>25720</x:v>
+        <x:v>26220</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7831</x:v>
+        <x:v>7861</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>398922</x:v>
+        <x:v>401452</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>334621</x:v>
+        <x:v>339121</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7861</x:v>
+        <x:v>7951</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>401452</x:v>
+        <x:v>406042</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>26220</x:v>
+        <x:v>26720</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>339121</x:v>
+        <x:v>371341</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>26220</x:v>
+        <x:v>26720</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>7951</x:v>
+        <x:v>8611</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>406042</x:v>
+        <x:v>439922</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>26720</x:v>
+        <x:v>27220</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>371341</x:v>
+        <x:v>400501</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>26720</x:v>
+        <x:v>27220</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2557,7 +2557,7 @@
       <x:c r="N40" s="56" t="s"/>
       <x:c r="O40" s="58" t="s"/>
       <x:c r="P40" s="60" t="n">
-        <x:v>101</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>8611</x:v>
+        <x:v>9181</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>439922</x:v>
+        <x:v>470702</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>400501</x:v>
+        <x:v>409501</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9181</x:v>
+        <x:v>9241</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>470702</x:v>
+        <x:v>479762</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>27220</x:v>
+        <x:v>28080</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>409501</x:v>
+        <x:v>421981</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>27220</x:v>
+        <x:v>28080</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9241</x:v>
+        <x:v>9571</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>479762</x:v>
+        <x:v>494292</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>421981</x:v>
+        <x:v>424981</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9571</x:v>
+        <x:v>9631</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>494292</x:v>
+        <x:v>497352</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>424981</x:v>
+        <x:v>427981</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9631</x:v>
+        <x:v>9691</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>497352</x:v>
+        <x:v>500412</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>28080</x:v>
+        <x:v>28760</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>427981</x:v>
+        <x:v>434641</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>28080</x:v>
+        <x:v>28760</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9691</x:v>
+        <x:v>9751</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>500412</x:v>
+        <x:v>508492</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>434641</x:v>
+        <x:v>437641</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9751</x:v>
+        <x:v>9811</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>508492</x:v>
+        <x:v>511552</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>28760</x:v>
+        <x:v>29120</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>437641</x:v>
+        <x:v>439081</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>28760</x:v>
+        <x:v>29120</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9811</x:v>
+        <x:v>9871</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>511552</x:v>
+        <x:v>513772</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>29120</x:v>
+        <x:v>29620</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>439081</x:v>
+        <x:v>441301</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>29120</x:v>
+        <x:v>29620</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9871</x:v>
+        <x:v>9931</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>513772</x:v>
+        <x:v>517052</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>441301</x:v>
+        <x:v>442801</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9931</x:v>
+        <x:v>9961</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>517052</x:v>
+        <x:v>518582</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>442801</x:v>
+        <x:v>444301</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9961</x:v>
+        <x:v>9991</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>518582</x:v>
+        <x:v>520112</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>29620</x:v>
+        <x:v>30120</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>444301</x:v>
+        <x:v>450301</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>29620</x:v>
+        <x:v>30120</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9991</x:v>
+        <x:v>10111</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>520112</x:v>
+        <x:v>527232</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>450301</x:v>
+        <x:v>451801</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10111</x:v>
+        <x:v>10141</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>527232</x:v>
+        <x:v>528762</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>451801</x:v>
+        <x:v>454801</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10141</x:v>
+        <x:v>10201</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>528762</x:v>
+        <x:v>531822</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>454801</x:v>
+        <x:v>456301</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10201</x:v>
+        <x:v>10231</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>531822</x:v>
+        <x:v>533352</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>456301</x:v>
+        <x:v>462301</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10231</x:v>
+        <x:v>10321</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>533352</x:v>
+        <x:v>539442</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>462301</x:v>
+        <x:v>477301</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10321</x:v>
+        <x:v>10621</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>539442</x:v>
+        <x:v>554742</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>477301</x:v>
+        <x:v>480301</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10621</x:v>
+        <x:v>10681</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>554742</x:v>
+        <x:v>557802</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>30120</x:v>
+        <x:v>31120</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>480301</x:v>
+        <x:v>483301</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>30120</x:v>
+        <x:v>31120</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10681</x:v>
+        <x:v>10741</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>557802</x:v>
+        <x:v>562862</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>31120</x:v>
+        <x:v>32120</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>483301</x:v>
+        <x:v>489301</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>31120</x:v>
+        <x:v>32120</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10741</x:v>
+        <x:v>10861</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>562862</x:v>
+        <x:v>570982</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>32120</x:v>
+        <x:v>32620</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>489301</x:v>
+        <x:v>490801</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>32120</x:v>
+        <x:v>32620</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10861</x:v>
+        <x:v>10891</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>570982</x:v>
+        <x:v>573512</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>490801</x:v>
+        <x:v>492301</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10891</x:v>
+        <x:v>10921</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>573512</x:v>
+        <x:v>575042</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>32620</x:v>
+        <x:v>34120</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>492301</x:v>
+        <x:v>499741</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>32620</x:v>
+        <x:v>34120</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10921</x:v>
+        <x:v>11071</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>575042</x:v>
+        <x:v>585632</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>34120</x:v>
+        <x:v>34300</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>499741</x:v>
+        <x:v>500461</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>34120</x:v>
+        <x:v>34300</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11071</x:v>
+        <x:v>11101</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>585632</x:v>
+        <x:v>586742</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>500461</x:v>
+        <x:v>501181</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>586742</x:v>
+        <x:v>587462</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>5086</x:v>
+        <x:v>5186</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11101</x:v>
+        <x:v>11131</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>587462</x:v>
+        <x:v>587592</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11131</x:v>
+        <x:v>11101</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>587592</x:v>
+        <x:v>587562</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>501181</x:v>
+        <x:v>504181</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>587562</x:v>
+        <x:v>590562</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>504181</x:v>
+        <x:v>510181</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>590562</x:v>
+        <x:v>596562</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>510181</x:v>
+        <x:v>514681</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>596562</x:v>
+        <x:v>601062</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>514681</x:v>
+        <x:v>523681</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11101</x:v>
+        <x:v>11341</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>601062</x:v>
+        <x:v>610302</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>34300</x:v>
+        <x:v>37800</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>523681</x:v>
+        <x:v>541681</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>34300</x:v>
+        <x:v>37800</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11341</x:v>
+        <x:v>11551</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>610302</x:v>
+        <x:v>635512</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>37800</x:v>
+        <x:v>38300</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>541681</x:v>
+        <x:v>543181</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>37800</x:v>
+        <x:v>38300</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11551</x:v>
+        <x:v>11581</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>635512</x:v>
+        <x:v>638042</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>543181</x:v>
+        <x:v>535681</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>638042</x:v>
+        <x:v>630542</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11581</x:v>
+        <x:v>11551</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>630542</x:v>
+        <x:v>630512</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>535681</x:v>
+        <x:v>555181</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11551</x:v>
+        <x:v>11941</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>630512</x:v>
+        <x:v>650402</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>38300</x:v>
+        <x:v>38800</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>555181</x:v>
+        <x:v>556681</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>38300</x:v>
+        <x:v>38800</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11941</x:v>
+        <x:v>11971</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>650402</x:v>
+        <x:v>652932</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>556681</x:v>
+        <x:v>557401</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11971</x:v>
+        <x:v>12001</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>652932</x:v>
+        <x:v>653682</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>557401</x:v>
+        <x:v>558901</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12001</x:v>
+        <x:v>12031</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>653682</x:v>
+        <x:v>655212</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>558901</x:v>
+        <x:v>561061</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12031</x:v>
+        <x:v>12061</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>655212</x:v>
+        <x:v>657402</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>561061</x:v>
+        <x:v>561781</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12061</x:v>
+        <x:v>12091</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>657402</x:v>
+        <x:v>658152</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>561781</x:v>
+        <x:v>569281</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12091</x:v>
+        <x:v>12241</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>658152</x:v>
+        <x:v>665802</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>569281</x:v>
+        <x:v>573781</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12241</x:v>
+        <x:v>12331</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>665802</x:v>
+        <x:v>670392</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>5186</x:v>
+        <x:v>5236</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>573781</x:v>
+        <x:v>575281</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12331</x:v>
+        <x:v>12391</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>670392</x:v>
+        <x:v>672002</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>5236</x:v>
+        <x:v>5332</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>38800</x:v>
+        <x:v>38980</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>38800</x:v>
+        <x:v>38980</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>672002</x:v>
+        <x:v>672458</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>38980</x:v>
+        <x:v>39980</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>575281</x:v>
+        <x:v>578281</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>38980</x:v>
+        <x:v>39980</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12391</x:v>
+        <x:v>12451</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>672458</x:v>
+        <x:v>677518</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>578281</x:v>
+        <x:v>579781</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12451</x:v>
+        <x:v>12481</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>677518</x:v>
+        <x:v>679048</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>579781</x:v>
+        <x:v>582781</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12481</x:v>
+        <x:v>12541</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>679048</x:v>
+        <x:v>682108</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>582781</x:v>
+        <x:v>584281</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12541</x:v>
+        <x:v>12571</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>682108</x:v>
+        <x:v>683638</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>39980</x:v>
+        <x:v>40480</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>584281</x:v>
+        <x:v>585781</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>39980</x:v>
+        <x:v>40480</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12571</x:v>
+        <x:v>12601</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>683638</x:v>
+        <x:v>686168</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>5332</x:v>
+        <x:v>5524</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>40480</x:v>
+        <x:v>41340</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>585781</x:v>
+        <x:v>588781</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>40480</x:v>
+        <x:v>41340</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12601</x:v>
+        <x:v>12661</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>686168</x:v>
+        <x:v>691140</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>41340</x:v>
+        <x:v>42340</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>588781</x:v>
+        <x:v>591781</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>41340</x:v>
+        <x:v>42340</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12661</x:v>
+        <x:v>12721</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>691140</x:v>
+        <x:v>696200</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>42340</x:v>
+        <x:v>42840</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>591781</x:v>
+        <x:v>593281</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>42340</x:v>
+        <x:v>42840</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12721</x:v>
+        <x:v>12751</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>696200</x:v>
+        <x:v>698730</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>42840</x:v>
+        <x:v>43340</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>593281</x:v>
+        <x:v>606781</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>42840</x:v>
+        <x:v>43340</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>12751</x:v>
+        <x:v>13021</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>698730</x:v>
+        <x:v>713500</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>43340</x:v>
+        <x:v>43840</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>606781</x:v>
+        <x:v>614281</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>43340</x:v>
+        <x:v>43840</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>13021</x:v>
+        <x:v>13171</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>713500</x:v>
+        <x:v>722150</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>614281</x:v>
+        <x:v>615781</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>13171</x:v>
+        <x:v>13201</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>722150</x:v>
+        <x:v>723680</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>615781</x:v>
+        <x:v>618781</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>13201</x:v>
+        <x:v>13261</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>723680</x:v>
+        <x:v>726740</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>43840</x:v>
+        <x:v>44340</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>618781</x:v>
+        <x:v>620281</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>43840</x:v>
+        <x:v>44340</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>13261</x:v>
+        <x:v>13291</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>726740</x:v>
+        <x:v>729270</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>620281</x:v>
+        <x:v>623281</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>729270</x:v>
+        <x:v>732270</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>623281</x:v>
+        <x:v>624001</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>13291</x:v>
+        <x:v>13321</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>732270</x:v>
+        <x:v>733020</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>624001</x:v>
+        <x:v>628441</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>13321</x:v>
+        <x:v>13411</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>733020</x:v>
+        <x:v>737550</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IV-A.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>44340</x:v>
+        <x:v>46840</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>628441</x:v>
+        <x:v>638941</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>44340</x:v>
+        <x:v>46840</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>13411</x:v>
+        <x:v>13621</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>737550</x:v>
+        <x:v>753260</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">
